--- a/artfynd/A 62610-2021 artfynd.xlsx
+++ b/artfynd/A 62610-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62610-2021 artfynd.xlsx
+++ b/artfynd/A 62610-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>93579968</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>832179.5487972314</v>
+        <v>832179</v>
       </c>
       <c r="R2" t="n">
-        <v>7433953.669358712</v>
+        <v>7433954</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,19 +758,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -828,15 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93580341</v>
+        <v>101573148</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,46 +824,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juoksuvaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>832179.5487972314</v>
+        <v>832161</v>
       </c>
       <c r="R3" t="n">
-        <v>7433953.669358712</v>
+        <v>7433975</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -910,22 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,43 +900,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Torr-frisk hed med tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101573148</v>
+        <v>101573658</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1006,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>832161.3438345176</v>
+        <v>832073</v>
       </c>
       <c r="R4" t="n">
-        <v>7433975.676087013</v>
+        <v>7434000</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1039,19 +994,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,19 +1023,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101573658</v>
+        <v>104187428</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1112,27 +1052,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>832072.8341969087</v>
+        <v>832010</v>
       </c>
       <c r="R5" t="n">
-        <v>7434000.201712498</v>
+        <v>7434058</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1156,22 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,22 +1113,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101573047</v>
+        <v>93579252</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,38 +1131,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>832166.9903486731</v>
+        <v>832228</v>
       </c>
       <c r="R6" t="n">
-        <v>7433981.532211808</v>
+        <v>7433941</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1272,22 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,34 +1211,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Torr-frisk hed med tall</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101572904</v>
+        <v>93580455</v>
       </c>
       <c r="B7" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,38 +1245,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>832191.2590694773</v>
+        <v>832074</v>
       </c>
       <c r="R7" t="n">
-        <v>7433974.968088562</v>
+        <v>7434005</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1389,22 +1307,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,34 +1321,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101573362</v>
+        <v>93580592</v>
       </c>
       <c r="B8" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,38 +1350,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>832138.0984836898</v>
+        <v>832026</v>
       </c>
       <c r="R8" t="n">
-        <v>7433980.379227472</v>
+        <v>7434032</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1506,22 +1416,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,34 +1430,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Torr-frisk hed med tall</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101573817</v>
+        <v>101573207</v>
       </c>
       <c r="B9" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,27 +1464,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1593,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>832044.8786377264</v>
+        <v>832159</v>
       </c>
       <c r="R9" t="n">
-        <v>7434001.150700669</v>
+        <v>7433975</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1626,19 +1529,14 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Större antal spillningshögar, bo med ägg som var kläckta mm i området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,7 +1545,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1666,15 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101573890</v>
+        <v>101573320</v>
       </c>
       <c r="B10" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,27 +1574,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1710,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>832029.7100624947</v>
+        <v>832161</v>
       </c>
       <c r="R10" t="n">
-        <v>7434004.85654773</v>
+        <v>7433991</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1743,28 +1639,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1783,15 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101573904</v>
+        <v>101573460</v>
       </c>
       <c r="B11" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,27 +1679,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1827,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>832016.6963466478</v>
+        <v>832116</v>
       </c>
       <c r="R11" t="n">
-        <v>7434026.704095345</v>
+        <v>7433973</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1860,28 +1740,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1900,15 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101573638</v>
+        <v>104187426</v>
       </c>
       <c r="B12" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,41 +1780,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>832084.8066879587</v>
+        <v>832227</v>
       </c>
       <c r="R12" t="n">
-        <v>7434009.612847351</v>
+        <v>7433955</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,22 +1834,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1998,7 +1848,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2010,50 +1859,49 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101573075</v>
+        <v>101581151</v>
       </c>
       <c r="B13" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>102622</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2061,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>832160.0724743705</v>
+        <v>832155</v>
       </c>
       <c r="R13" t="n">
-        <v>7433976.315049629</v>
+        <v>7433993</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2094,28 +1942,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2134,57 +1971,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101574015</v>
+        <v>104187427</v>
       </c>
       <c r="B14" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>832000.2302484489</v>
+        <v>831969</v>
       </c>
       <c r="R14" t="n">
-        <v>7434057.266530139</v>
+        <v>7434086</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2208,22 +2036,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,7 +2050,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2244,22 +2061,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101573805</v>
+        <v>93580341</v>
       </c>
       <c r="B15" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,21 +2096,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>832072.8341969087</v>
+        <v>832179</v>
       </c>
       <c r="R15" t="n">
-        <v>7434000.201712498</v>
+        <v>7433954</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2325,22 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,30 +2163,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Torr-frisk hed med tall</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101572930</v>
+        <v>101572572</v>
       </c>
       <c r="B16" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>832177.9309119864</v>
+        <v>832213</v>
       </c>
       <c r="R16" t="n">
-        <v>7433989.625647712</v>
+        <v>7433924</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2445,19 +2255,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,15 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101573197</v>
+        <v>101572686</v>
       </c>
       <c r="B17" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>832159.0886217253</v>
+        <v>832217</v>
       </c>
       <c r="R17" t="n">
-        <v>7433974.605412493</v>
+        <v>7433930</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2562,19 +2357,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,53 +2387,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104187428</v>
+        <v>101572726</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>832010.0259737212</v>
+        <v>832195</v>
       </c>
       <c r="R18" t="n">
-        <v>7434058.46517474</v>
+        <v>7433938</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2672,22 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,6 +2470,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2707,10 +2482,1336 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>101572904</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>832191</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7433975</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Maj Aspebo</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>101572930</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>832178</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7433989</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>101573047</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>832167</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7433982</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>101573075</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>832160</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7433977</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>101573197</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>832159</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7433975</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>101573362</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>832139</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7433980</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>101573638</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>832084</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7434010</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>101573805</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>832073</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7434000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>101573817</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>832044</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7434001</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>101573890</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>832029</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7434004</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>101573904</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>832016</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7434027</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>101574015</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>832000</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7434057</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>101574062</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>831977</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7434101</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62610-2021 artfynd.xlsx
+++ b/artfynd/A 62610-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -810,6 +815,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93579968</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187428</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93579252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93580455</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93580592</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573207</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573320</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573460</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187426</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101581151</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187427</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93580341</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101572572</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101572686</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101572726</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101572904</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2690,6 +2785,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101572930</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573047</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2894,6 +2999,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573075</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2996,6 +3106,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573197</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3098,6 +3213,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573362</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3200,6 +3320,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573638</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3302,6 +3427,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573805</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3404,6 +3534,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573817</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3506,6 +3641,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573890</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3608,6 +3748,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101573904</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3710,6 +3855,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101574015</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3812,8 +3962,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101574062</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>